--- a/reports/devops-juniors-israel-2026-W32.xlsx
+++ b/reports/devops-juniors-israel-2026-W32.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03T10:10:19</t>
+    <t xml:space="preserve">2026-08-04T08:52:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -160,813 +160,1029 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-gambit-security-4447659163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">Check Point Software</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4446847161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4431915164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
   </si>
   <si>
     <t xml:space="preserve">Unilink Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galooli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-e2e-solutions-il-4446785033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 24376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-24376-at-comblack-4446756706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enlight Renewable Energy Ltd (ENLT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-enlight-renewable-energy-ltd-enlt-4442705417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4444112385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (35966 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYMOTIVE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (36711 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-36711-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446747246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4444112385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (35966 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -976,7 +1192,10 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
@@ -985,6 +1204,15 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Git</t>
   </si>
   <si>
@@ -995,24 +1223,6 @@
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1170,7 +1380,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1178,7 +1388,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1194,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10">
@@ -1276,7 +1486,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1284,7 +1494,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1292,7 +1502,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1300,7 +1510,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1318,7 +1528,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
@@ -1338,7 +1548,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1423,25 +1633,25 @@
         <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -1449,13 +1659,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1464,16 +1674,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1481,13 +1691,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1551,25 +1761,25 @@
         <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1577,31 +1787,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1609,31 +1819,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1641,31 +1851,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1673,25 +1883,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>97</v>
@@ -1711,13 +1921,13 @@
         <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>101</v>
@@ -1729,7 +1939,7 @@
         <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -1737,31 +1947,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>60</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="3">
-        <v>74</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
@@ -1769,31 +1979,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="3">
-        <v>70</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1801,31 +2011,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -1833,31 +2043,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -1865,31 +2075,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -1897,31 +2107,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1929,31 +2139,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1961,31 +2171,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -1993,31 +2203,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
@@ -2025,31 +2235,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -2057,31 +2267,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24">
@@ -2089,31 +2299,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
@@ -2121,31 +2331,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26">
@@ -2153,31 +2363,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2216,8 +2426,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2230,7 +2440,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2245,22 +2455,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2283,7 +2493,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
@@ -2295,7 +2505,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -2306,42 +2516,42 @@
         <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2350,33 +2560,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K4" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2388,7 +2598,7 @@
         <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -2400,7 +2610,7 @@
         <v>64</v>
       </c>
       <c r="K5" s="3">
-        <v>71</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2423,7 +2633,7 @@
         <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
@@ -2435,7 +2645,7 @@
         <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -2446,162 +2656,162 @@
         <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>97</v>
@@ -2610,7 +2820,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -2621,19 +2831,19 @@
         <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
@@ -2642,1477 +2852,1477 @@
         <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="K12" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>60</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="3">
-        <v>74</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="3">
-        <v>70</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="K14" s="3">
-        <v>13</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K15" s="3">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K17" s="3">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>35</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K21" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="K23" s="3">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="K24" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K25" s="3">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K26" s="3">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="K27" s="3">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>92</v>
+        <v>187</v>
       </c>
       <c r="K28" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K29" s="3">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K30" s="3">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="K32" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>49</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
+        <v>23</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" s="3">
         <v>20</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K34" s="3">
-        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>92</v>
+        <v>218</v>
       </c>
       <c r="K35" s="3">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="K36" s="3">
-        <v>11</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="K37" s="3">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="K38" s="3">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="K39" s="3">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="K40" s="3">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="K41" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>236</v>
+        <v>179</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="K42" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="K43" s="3">
-        <v>71</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>50</v>
+        <v>256</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="K44" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>222</v>
+        <v>72</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K45" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>177</v>
+        <v>265</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="K46" s="3">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="K47" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>259</v>
+        <v>61</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="K48" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>244</v>
+        <v>65</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E49" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>248</v>
+        <v>165</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>89</v>
+        <v>283</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>248</v>
+        <v>52</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>94</v>
+        <v>287</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="K51" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="K52" s="3">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>232</v>
+        <v>67</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>53</v>
+        <v>296</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>287</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>157</v>
+        <v>288</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="K54" s="3">
         <v>19</v>
@@ -4120,142 +4330,807 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>291</v>
+        <v>67</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>294</v>
+        <v>52</v>
       </c>
       <c r="K55" s="3">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="K56" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>301</v>
+        <v>67</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="G57" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="K57" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K58" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K59" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K60" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K61" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K62" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K63" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>6</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K64" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>6</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K65" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E67" s="3">
+        <v>4</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="K67" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="3">
+        <v>4</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="K68" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="K69" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="K70" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="K58" s="3">
-        <v>70</v>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="K72" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K73" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K74" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K75" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="K76" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K77" s="3">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K58"/>
+  <autoFilter ref="A1:K77"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4314,6 +5189,25 @@
     <hyperlink ref="I56" r:id="rId55"/>
     <hyperlink ref="I57" r:id="rId56"/>
     <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4321,9 +5215,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4344,10 +5238,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -4355,55 +5249,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4418,178 +5384,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>308</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>284</v>
+        <v>351</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>309</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>342</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>310</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>311</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>312</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>314</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>315</v>
+        <v>384</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>316</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>386</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>317</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>319</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>297</v>
+        <v>390</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>320</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>321</v>
+        <v>392</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>322</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>323</v>
+        <v>394</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>324</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>325</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>326</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>328</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>329</v>
+        <v>399</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>331</v>
+        <v>401</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -4609,10 +5575,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
@@ -4620,10 +5586,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>335</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
@@ -4631,10 +5597,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
@@ -4642,10 +5608,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
@@ -4653,10 +5619,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4677,13 +5643,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>409</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>341</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
@@ -4694,7 +5660,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4703,22 +5669,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>343</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W32.xlsx
+++ b/reports/devops-juniors-israel-2026-W32.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="416">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04T08:52:32</t>
+    <t xml:space="preserve">2026-08-05T08:50:02</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -112,6 +112,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -193,834 +196,837 @@
     <t xml:space="preserve">2026-08-03</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives Intralogistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-gambit-security-4447659163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seemplicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36620 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446723677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
   </si>
   <si>
     <t xml:space="preserve">RAD</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4445499098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (35966 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYMOTIVE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-gotfriends-4445849138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-gambit-security-4447659163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4431915164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (34817 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galooli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4444112385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (35966 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYMOTIVE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Technician (36711 )</t>
   </si>
   <si>
@@ -1039,6 +1045,21 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst (Student Position)</t>
   </si>
   <si>
@@ -1090,15 +1111,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
   </si>
   <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Technician</t>
   </si>
   <si>
@@ -1114,15 +1126,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German)</t>
   </si>
   <si>
@@ -1141,7 +1144,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1159,33 +1171,30 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
@@ -1204,27 +1213,27 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1253,9 +1262,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1386,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -1388,7 +1394,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1404,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10">
@@ -1486,7 +1492,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1508,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -1537,6 +1543,14 @@
       </c>
       <c r="B28" s="3">
         <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1548,7 +1562,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1560,34 +1574,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -1595,13 +1609,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
@@ -1610,16 +1624,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1627,13 +1641,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
@@ -1642,16 +1656,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -1659,13 +1673,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1674,16 +1688,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1691,13 +1705,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1706,16 +1720,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1723,31 +1737,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1755,13 +1769,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1770,16 +1784,16 @@
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1825,25 +1839,25 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>81</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1851,31 +1865,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
         <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1883,31 +1897,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -1915,31 +1929,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>74</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>68</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -1947,31 +1961,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>60</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="14">
@@ -1979,31 +1993,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>70</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="3">
-        <v>57</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -2011,31 +2025,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -2043,31 +2057,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
@@ -2075,31 +2089,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
@@ -2107,31 +2121,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
@@ -2139,31 +2153,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
@@ -2171,31 +2185,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -2203,31 +2217,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22">
@@ -2235,31 +2249,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
@@ -2267,31 +2281,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="3">
+        <v>40</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>37</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="24">
@@ -2299,31 +2313,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3">
+        <v>40</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>37</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="25">
@@ -2331,19 +2345,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>163</v>
@@ -2366,28 +2380,28 @@
         <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>37</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>32</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2426,8 +2440,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2440,48 +2454,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>28</v>
@@ -2490,33 +2504,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>26</v>
@@ -2525,33 +2539,33 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2560,33 +2574,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2595,68 +2609,68 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
@@ -2665,22 +2679,22 @@
         <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2703,7 +2717,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2715,7 +2729,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2726,579 +2740,579 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>80</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>81</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="K9" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
         <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K10" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>74</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>68</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="K12" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>70</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3">
+        <v>70</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3">
-        <v>57</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K14" s="3">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K15" s="3">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K16" s="3">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K17" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K19" s="3">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="K20" s="3">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="K21" s="3">
-        <v>28</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K22" s="3">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="3">
+        <v>40</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>37</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>40</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>37</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="K24" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
@@ -3310,7 +3324,7 @@
         <v>165</v>
       </c>
       <c r="K25" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3318,45 +3332,45 @@
         <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>37</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>32</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K26" s="3">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
@@ -3365,22 +3379,22 @@
         <v>32</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K27" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -3403,7 +3417,7 @@
         <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
@@ -3412,21 +3426,21 @@
         <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="K28" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3435,33 +3449,33 @@
         <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="K29" s="3">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3470,57 +3484,57 @@
         <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K30" s="3">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="K31" s="3">
-        <v>14</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32">
@@ -3528,104 +3542,104 @@
         <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>111</v>
+        <v>205</v>
       </c>
       <c r="K32" s="3">
-        <v>81</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>205</v>
+        <v>62</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="K33" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>213</v>
+        <v>117</v>
       </c>
       <c r="K34" s="3">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
@@ -3636,7 +3650,7 @@
         <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3645,22 +3659,22 @@
         <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="K35" s="3">
-        <v>76</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -3671,54 +3685,54 @@
         <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="K36" s="3">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>226</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
@@ -3727,10 +3741,10 @@
         <v>227</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="K37" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
@@ -3741,7 +3755,7 @@
         <v>229</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3750,33 +3764,33 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3785,103 +3799,103 @@
         <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>93</v>
+        <v>238</v>
       </c>
       <c r="K39" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="K40" s="3">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="K41" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>179</v>
+        <v>249</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3890,33 +3904,33 @@
         <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K42" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3925,33 +3939,33 @@
         <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K43" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3960,115 +3974,115 @@
         <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>258</v>
+        <v>195</v>
       </c>
       <c r="K44" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>72</v>
+        <v>263</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="3">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" s="3">
-        <v>13</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="K45" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>265</v>
+        <v>67</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E46" s="3">
         <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K46" s="3">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>269</v>
+        <v>150</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E47" s="3">
         <v>13</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
@@ -4077,10 +4091,10 @@
         <v>272</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>213</v>
+        <v>53</v>
       </c>
       <c r="K47" s="3">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48">
@@ -4088,185 +4102,185 @@
         <v>273</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>274</v>
+        <v>150</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3">
         <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="K48" s="3">
-        <v>26</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>65</v>
+        <v>276</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="3">
+        <v>13</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" s="3">
-        <v>12</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="K49" s="3">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="K50" s="3">
-        <v>72</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>291</v>
+        <v>108</v>
       </c>
       <c r="K51" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>264</v>
+        <v>60</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E52" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="K52" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4275,22 +4289,22 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>296</v>
+        <v>53</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
@@ -4298,10 +4312,10 @@
         <v>297</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4310,19 +4324,19 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>93</v>
+        <v>302</v>
       </c>
       <c r="K54" s="3">
         <v>19</v>
@@ -4330,13 +4344,13 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>89</v>
+        <v>279</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>67</v>
+        <v>289</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4348,30 +4362,30 @@
         <v>300</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="K55" s="3">
-        <v>72</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4380,33 +4394,33 @@
         <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="K56" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>67</v>
+        <v>299</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4415,22 +4429,22 @@
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -4438,150 +4452,150 @@
         <v>310</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>145</v>
+        <v>311</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="J58" s="3" t="s">
-        <v>277</v>
+        <v>92</v>
       </c>
       <c r="K58" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>314</v>
+        <v>96</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>317</v>
+        <v>53</v>
       </c>
       <c r="K59" s="3">
-        <v>57</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>244</v>
+        <v>316</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>318</v>
+        <v>201</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K60" s="3">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="J61" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="K61" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>325</v>
+        <v>211</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4590,33 +4604,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>93</v>
+        <v>278</v>
       </c>
       <c r="K62" s="3">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4625,10 +4639,10 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
@@ -4637,21 +4651,21 @@
         <v>328</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>296</v>
+        <v>199</v>
       </c>
       <c r="K63" s="3">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>329</v>
+        <v>201</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4660,10 +4674,10 @@
         <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -4672,21 +4686,21 @@
         <v>330</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>253</v>
+        <v>307</v>
       </c>
       <c r="K64" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="C65" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4695,33 +4709,33 @@
         <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>334</v>
+        <v>195</v>
       </c>
       <c r="K65" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4730,10 +4744,10 @@
         <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>30</v>
@@ -4742,10 +4756,10 @@
         <v>336</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -4753,150 +4767,150 @@
         <v>337</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="J67" s="3" t="s">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="K67" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E68" s="3">
         <v>4</v>
       </c>
       <c r="F68" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="K68" s="3">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
+      <c r="G69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I69" s="3" t="s">
+      <c r="J69" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="K69" s="3">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="3">
+        <v>4</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="G70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="J70" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="K70" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>355</v>
+        <v>202</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4905,33 +4919,33 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>133</v>
+        <v>355</v>
       </c>
       <c r="K71" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>130</v>
+        <v>319</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4940,19 +4954,19 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="K72" s="3">
         <v>22</v>
@@ -4960,13 +4974,13 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4975,33 +4989,33 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="K73" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>188</v>
+        <v>365</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>25</v>
@@ -5010,33 +5024,33 @@
         <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="K74" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>366</v>
+        <v>187</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>25</v>
@@ -5045,33 +5059,33 @@
         <v>3</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K75" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>27</v>
@@ -5081,30 +5095,30 @@
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>334</v>
+        <v>92</v>
       </c>
       <c r="K76" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>27</v>
@@ -5114,23 +5128,56 @@
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="K77" s="3">
-        <v>71</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K78" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K77"/>
+  <autoFilter ref="A1:K78"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5208,6 +5255,7 @@
     <hyperlink ref="I75" r:id="rId74"/>
     <hyperlink ref="I76" r:id="rId75"/>
     <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5215,9 +5263,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5226,150 +5274,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>228</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>229</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>230</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>231</v>
+        <v>379</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5384,178 +5382,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3">
         <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>338</v>
+        <v>385</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>261</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>386</v>
+        <v>268</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B10" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -5572,13 +5570,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
@@ -5586,10 +5584,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3">
@@ -5600,7 +5598,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
@@ -5608,10 +5606,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5">
@@ -5622,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5640,16 +5638,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
@@ -5660,7 +5658,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5669,22 +5667,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W32.xlsx
+++ b/reports/devops-juniors-israel-2026-W32.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05T08:50:02</t>
+    <t xml:space="preserve">2026-08-06T08:51:29</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -112,1156 +112,1084 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack you'll work with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Seen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/ת סיסטם עם אוריינטציה ללינוקס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SrvIT - Managed Secure IT Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazkeret Batya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%A2%D7%9D-%D7%90%D7%95%D7%A8%D7%99%D7%99%D7%A0%D7%98%D7%A6%D7%99%D7%94-%D7%9C%D7%9C%D7%99%D7%A0%D7%95%D7%A7%D7%A1-at-srvit-managed-secure-it-services-4448079212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seemplicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-e2e-solutions-il-4446785033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Technologies, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (34817 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (35966 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYMOTIVE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (36711 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-36711-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446747246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack you'll work with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apply URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Seen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives Intralogistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-gambit-security-4447659163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seemplicity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446723677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-experis-israel-4442821565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4445499098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (34817 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (35966 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYMOTIVE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-cymotive-technologies-4445985696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (36711 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-36711-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446747246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1394,7 +1322,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1330,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1410,7 +1338,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="10">
@@ -1492,7 +1420,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -1508,7 +1436,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1516,7 +1444,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1534,7 +1462,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
@@ -1543,14 +1471,6 @@
       </c>
       <c r="B28" s="3">
         <v>9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1574,34 +1494,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -1609,13 +1529,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>28</v>
@@ -1624,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1641,13 +1561,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>26</v>
@@ -1656,16 +1576,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -1673,13 +1593,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1688,16 +1608,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1705,13 +1625,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1720,16 +1640,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1737,31 +1657,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3">
-        <v>92</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1769,13 +1689,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1784,16 +1704,16 @@
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1813,19 +1733,19 @@
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -1833,31 +1753,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1865,31 +1785,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1897,31 +1817,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -1929,31 +1849,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -1961,31 +1881,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1993,31 +1913,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -2025,31 +1945,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -2057,31 +1977,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -2089,31 +2009,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -2121,31 +2041,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -2153,31 +2073,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -2185,31 +2105,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -2217,13 +2137,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
@@ -2232,16 +2152,16 @@
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -2249,13 +2169,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -2264,16 +2184,16 @@
         <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -2281,31 +2201,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
@@ -2313,13 +2233,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
@@ -2328,16 +2248,16 @@
         <v>40</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -2345,31 +2265,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -2377,13 +2297,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2392,16 +2312,16 @@
         <v>37</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2440,8 +2360,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2454,48 +2374,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>28</v>
@@ -2504,33 +2424,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K2" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>26</v>
@@ -2539,33 +2459,33 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="K3" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2574,33 +2494,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2609,68 +2529,68 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K5" s="3">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
-        <v>92</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K6" s="3">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
@@ -2679,22 +2599,22 @@
         <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K7" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2711,337 +2631,337 @@
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="K11" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K14" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K15" s="3">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
         <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K17" s="3">
         <v>37</v>
@@ -3049,118 +2969,118 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
@@ -3169,33 +3089,33 @@
         <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="K21" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -3204,68 +3124,68 @@
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="K22" s="3">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K23" s="3">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
@@ -3274,68 +3194,68 @@
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K25" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -3344,103 +3264,103 @@
         <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K27" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3449,33 +3369,33 @@
         <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="K29" s="3">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3484,33 +3404,33 @@
         <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="K30" s="3">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3519,103 +3439,103 @@
         <v>30</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>199</v>
+        <v>143</v>
       </c>
       <c r="K31" s="3">
-        <v>66</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="3">
-        <v>28</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K32" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>24</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3">
-        <v>27</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K33" s="3">
-        <v>15</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
@@ -3624,33 +3544,33 @@
         <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="K34" s="3">
-        <v>82</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3659,33 +3579,33 @@
         <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="K35" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3694,33 +3614,33 @@
         <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="K36" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3729,68 +3649,68 @@
         <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="K37" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>230</v>
+        <v>67</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="K38" s="3">
-        <v>82</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3799,173 +3719,173 @@
         <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="K39" s="3">
-        <v>17</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
         <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="K40" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
         <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>165</v>
+        <v>87</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>20</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>17</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="K42" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="K43" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3974,33 +3894,33 @@
         <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="K44" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -4012,205 +3932,205 @@
         <v>260</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>267</v>
+        <v>90</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="K46" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="K47" s="3">
-        <v>73</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>150</v>
+        <v>269</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>151</v>
+        <v>270</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>275</v>
+        <v>163</v>
       </c>
       <c r="K48" s="3">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>278</v>
+        <v>143</v>
       </c>
       <c r="K49" s="3">
-        <v>58</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>280</v>
+        <v>72</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>178</v>
+        <v>277</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E50" s="3">
         <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>112</v>
+        <v>280</v>
       </c>
       <c r="K50" s="3">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>285</v>
+        <v>250</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4219,103 +4139,103 @@
         <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K51" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="3">
-        <v>12</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="J52" s="3" t="s">
-        <v>291</v>
+        <v>102</v>
       </c>
       <c r="K52" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>13</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>10</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="K53" s="3">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4324,33 +4244,33 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>302</v>
+        <v>52</v>
       </c>
       <c r="K54" s="3">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>289</v>
+        <v>113</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4362,30 +4282,30 @@
         <v>300</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="K55" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4397,30 +4317,30 @@
         <v>300</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K56" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4432,30 +4352,30 @@
         <v>300</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K57" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>310</v>
+        <v>103</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4464,33 +4384,33 @@
         <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="K58" s="3">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>96</v>
+        <v>310</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4499,92 +4419,92 @@
         <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="K59" s="3">
-        <v>73</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>316</v>
+        <v>265</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>201</v>
+        <v>313</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="K60" s="3">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" s="3">
-        <v>8</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="K61" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -4592,10 +4512,10 @@
         <v>262</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>211</v>
+        <v>319</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4604,33 +4524,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>278</v>
+        <v>143</v>
       </c>
       <c r="K62" s="3">
-        <v>58</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>253</v>
+        <v>321</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>326</v>
+        <v>61</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4639,33 +4559,33 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>199</v>
+        <v>324</v>
       </c>
       <c r="K63" s="3">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>201</v>
+        <v>311</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>202</v>
+        <v>90</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4674,115 +4594,115 @@
         <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>307</v>
+        <v>138</v>
       </c>
       <c r="K64" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E65" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="K65" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="G66" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>6</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>336</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="K66" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>6</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="G67" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>30</v>
@@ -4791,393 +4711,152 @@
         <v>338</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>165</v>
+        <v>339</v>
       </c>
       <c r="K67" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68" s="3">
-        <v>4</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="K68" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>225</v>
+        <v>151</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E69" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>347</v>
+        <v>102</v>
       </c>
       <c r="K69" s="3">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="C70" s="3" t="s">
-        <v>335</v>
+        <v>135</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E70" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="J70" s="3" t="s">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="K70" s="3">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="D71" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>354</v>
-      </c>
       <c r="J71" s="3" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="K71" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K72" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K73" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K74" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K75" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K76" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77" s="3">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K77" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K78" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K78"/>
+  <autoFilter ref="A1:K71"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5249,13 +4928,6 @@
     <hyperlink ref="I69" r:id="rId68"/>
     <hyperlink ref="I70" r:id="rId69"/>
     <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5263,9 +4935,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5274,56 +4946,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -5332,42 +5004,68 @@
         <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>262</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>377</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>379</v>
+        <v>264</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>160</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5382,178 +5080,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B6" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="B7" s="3">
         <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>268</v>
+        <v>342</v>
       </c>
       <c r="B8" s="3">
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="B9" s="3">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>397</v>
+        <v>333</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="B14" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -5570,13 +5268,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -5584,10 +5282,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3">
@@ -5598,7 +5296,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4">
@@ -5606,10 +5304,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
@@ -5617,10 +5315,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -5638,16 +5336,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2">
@@ -5658,7 +5356,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5667,22 +5365,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>391</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W32.xlsx
+++ b/reports/devops-juniors-israel-2026-W32.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="398">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-06T08:51:29</t>
+    <t xml:space="preserve">2026-08-07T07:38:25</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -262,6 +262,36 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer 24246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-24246-at-comblack-4450246628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Terraform/IaC, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-peak-innovation-4450276163</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
@@ -280,570 +310,564 @@
     <t xml:space="preserve">2026-07-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGILINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seemplicity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (36859)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-36859-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4450236665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGILINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-agilina-4448561239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/ת סיסטם עם אוריינטציה ללינוקס</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SrvIT - Managed Secure IT Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazkeret Batya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%A2%D7%9D-%D7%90%D7%95%D7%A8%D7%99%D7%99%D7%A0%D7%98%D7%A6%D7%99%D7%94-%D7%9C%D7%9C%D7%99%D7%A0%D7%95%D7%A7%D7%A1-at-srvit-managed-secure-it-services-4448079212</t>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seemplicity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-at-seemplicity-4445609263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-yael-korentec-technologies-4450212903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
   </si>
   <si>
     <t xml:space="preserve">Hadera, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-e2e-solutions-il-4446785033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-check-point-software-4443373234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4447384198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
   </si>
   <si>
+    <t xml:space="preserve">Integress, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-integress-inc-4449148474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
   </si>
   <si>
@@ -871,18 +895,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
   </si>
   <si>
@@ -946,13 +958,25 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Technician (34817 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-34817-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446725424</t>
+    <t xml:space="preserve">Customer Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galooli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer #1353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-%231353-at-rad-4450239123</t>
   </si>
   <si>
     <t xml:space="preserve">WSC Sports</t>
@@ -970,7 +994,7 @@
     <t xml:space="preserve">Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446732428</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-35966-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4450223565</t>
   </si>
   <si>
     <t xml:space="preserve">CYMOTIVE Technologies</t>
@@ -991,12 +1015,6 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Technician (36711 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-36711-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446747246</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -1036,9 +1054,6 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
   </si>
   <si>
@@ -1060,10 +1075,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
   </si>
   <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4444118425</t>
   </si>
   <si>
     <t xml:space="preserve">Working Student, Legal (German)</t>
@@ -1114,10 +1132,10 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
@@ -1322,7 +1340,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1330,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1338,7 +1356,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10">
@@ -1420,7 +1438,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1428,7 +1446,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1762,16 +1780,16 @@
         <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>86</v>
@@ -1791,25 +1809,25 @@
         <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3">
+        <v>88</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
-        <v>81</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -1817,31 +1835,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3">
+        <v>83</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="3">
-        <v>80</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -1855,13 +1873,13 @@
         <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>100</v>
@@ -1873,7 +1891,7 @@
         <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -1881,31 +1899,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>76</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>74</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1913,13 +1931,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
@@ -1928,16 +1946,16 @@
         <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -2041,13 +2059,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -2056,16 +2074,16 @@
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -2073,13 +2091,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
@@ -2111,19 +2129,19 @@
         <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>142</v>
@@ -2143,25 +2161,25 @@
         <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
@@ -2175,7 +2193,7 @@
         <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -2184,16 +2202,16 @@
         <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="23">
@@ -2201,19 +2219,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>156</v>
@@ -2233,31 +2251,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
         <v>40</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -2265,19 +2283,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>165</v>
@@ -2297,10 +2315,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>67</v>
@@ -2309,19 +2327,19 @@
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2374,7 +2392,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2389,22 +2407,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2427,7 +2445,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
@@ -2439,7 +2457,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -2462,7 +2480,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2474,7 +2492,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -2497,7 +2515,7 @@
         <v>56</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
@@ -2509,7 +2527,7 @@
         <v>58</v>
       </c>
       <c r="K4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2532,7 +2550,7 @@
         <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -2544,7 +2562,7 @@
         <v>64</v>
       </c>
       <c r="K5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2567,7 +2585,7 @@
         <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
@@ -2579,7 +2597,7 @@
         <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -2602,7 +2620,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2614,7 +2632,7 @@
         <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2637,7 +2655,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -2649,7 +2667,7 @@
         <v>58</v>
       </c>
       <c r="K8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2663,19 +2681,19 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>86</v>
@@ -2684,7 +2702,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2695,66 +2713,66 @@
         <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>88</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>81</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K10" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3">
+        <v>83</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="3">
-        <v>80</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -2765,19 +2783,19 @@
         <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>30</v>
@@ -2786,56 +2804,56 @@
         <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="K12" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>76</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>74</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K13" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
@@ -2844,22 +2862,22 @@
         <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -2882,7 +2900,7 @@
         <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>30</v>
@@ -2894,7 +2912,7 @@
         <v>116</v>
       </c>
       <c r="K15" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2917,7 +2935,7 @@
         <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
@@ -2929,7 +2947,7 @@
         <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -2952,7 +2970,7 @@
         <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
@@ -2964,18 +2982,18 @@
         <v>127</v>
       </c>
       <c r="K17" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2984,33 +3002,33 @@
         <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
@@ -3022,7 +3040,7 @@
         <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
@@ -3034,7 +3052,7 @@
         <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -3045,22 +3063,22 @@
         <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>142</v>
@@ -3069,7 +3087,7 @@
         <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>6</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -3080,31 +3098,31 @@
         <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
         <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="K21" s="3">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -3115,7 +3133,7 @@
         <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -3124,45 +3142,45 @@
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="K22" s="3">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
@@ -3174,65 +3192,65 @@
         <v>158</v>
       </c>
       <c r="K23" s="3">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>30</v>
@@ -3244,15 +3262,15 @@
         <v>167</v>
       </c>
       <c r="K25" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>67</v>
@@ -3261,316 +3279,316 @@
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="K26" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>30</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>36</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>30</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>34</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="K28" s="3">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>30</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>30</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>193</v>
+        <v>138</v>
       </c>
       <c r="K29" s="3">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>24</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>30</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K31" s="3">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>27</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="K32" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>23</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>24</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="K33" s="3">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>145</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>210</v>
+        <v>146</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="K34" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3579,33 +3597,33 @@
         <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="K35" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3614,33 +3632,33 @@
         <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="K36" s="3">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3649,22 +3667,22 @@
         <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="K37" s="3">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -3675,42 +3693,42 @@
         <v>225</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>67</v>
+        <v>226</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="K38" s="3">
-        <v>36</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3719,33 +3737,33 @@
         <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="K39" s="3">
-        <v>83</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3754,138 +3772,138 @@
         <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K40" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>87</v>
+        <v>246</v>
       </c>
       <c r="K41" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="K42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="K43" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>255</v>
+        <v>84</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3894,33 +3912,33 @@
         <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3929,33 +3947,33 @@
         <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>64</v>
+        <v>264</v>
       </c>
       <c r="K45" s="3">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>89</v>
+        <v>266</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>90</v>
+        <v>267</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3964,19 +3982,19 @@
         <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3984,13 +4002,13 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3999,33 +4017,33 @@
         <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>268</v>
+        <v>158</v>
       </c>
       <c r="K47" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4037,30 +4055,30 @@
         <v>271</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4069,103 +4087,103 @@
         <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="K49" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>72</v>
+        <v>282</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="K50" s="3">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E51" s="3">
         <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="K51" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4174,30 +4192,30 @@
         <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K52" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>67</v>
@@ -4209,33 +4227,33 @@
         <v>13</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4244,30 +4262,30 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K54" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>113</v>
@@ -4279,30 +4297,30 @@
         <v>10</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="K55" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>67</v>
@@ -4314,30 +4332,30 @@
         <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K56" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>113</v>
@@ -4349,30 +4367,30 @@
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>107</v>
+        <v>246</v>
       </c>
       <c r="K57" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>67</v>
@@ -4384,33 +4402,33 @@
         <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K58" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4419,68 +4437,68 @@
         <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>143</v>
+        <v>318</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="K60" s="3">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4489,33 +4507,33 @@
         <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>304</v>
+        <v>182</v>
       </c>
       <c r="K61" s="3">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>319</v>
+        <v>200</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4524,33 +4542,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="K62" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4559,33 +4577,33 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>324</v>
+        <v>138</v>
       </c>
       <c r="K63" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4594,33 +4612,33 @@
         <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="K64" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>27</v>
@@ -4629,33 +4647,33 @@
         <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>116</v>
       </c>
       <c r="K65" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4664,33 +4682,33 @@
         <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>138</v>
+        <v>240</v>
       </c>
       <c r="K66" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4699,33 +4717,33 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="K67" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>340</v>
+        <v>265</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4734,33 +4752,33 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="K68" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4769,33 +4787,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K69" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>189</v>
+        <v>353</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4804,33 +4822,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>188</v>
+        <v>308</v>
       </c>
       <c r="K70" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>27</v>
@@ -4840,19 +4858,19 @@
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K71" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4935,8 +4953,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4958,10 +4976,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -4969,103 +4987,175 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>254</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>256</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>199</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>184</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>184</v>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5080,178 +5170,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B4" s="3">
         <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B5" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="B8" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
       <c r="B9" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -5271,10 +5361,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
@@ -5282,10 +5372,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3">
@@ -5293,10 +5383,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -5307,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5">
@@ -5318,7 +5408,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -5339,13 +5429,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2">
@@ -5356,7 +5446,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5368,19 +5458,19 @@
         <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W32.xlsx
+++ b/reports/devops-juniors-israel-2026-W32.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="402">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07T07:38:25</t>
+    <t xml:space="preserve">2026-08-09T07:10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -175,19 +175,16 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calanit by one</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4448158765</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-03</t>
@@ -463,6 +460,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
   </si>
   <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peax-dorcom-4449295580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
   </si>
   <si>
@@ -520,6 +529,24 @@
     <t xml:space="preserve">2026-07-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ZyG</t>
   </si>
   <si>
@@ -532,24 +559,6 @@
     <t xml:space="preserve">2026-07-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Specialist</t>
   </si>
   <si>
@@ -895,6 +904,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
   </si>
   <si>
+    <t xml:space="preserve">Veridis Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-veridis-environment-4448755673</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
   </si>
   <si>
@@ -922,30 +940,24 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">SISL Global</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
   </si>
   <si>
@@ -1048,21 +1060,21 @@
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Support Technician</t>
   </si>
   <si>
@@ -1132,25 +1144,25 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
@@ -1332,7 +1344,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1340,7 +1352,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1348,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1356,7 +1368,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10">
@@ -1446,7 +1458,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1480,7 +1492,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
@@ -1611,13 +1623,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1626,16 +1638,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -1643,13 +1655,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1658,16 +1670,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -1675,13 +1687,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
@@ -1690,16 +1702,16 @@
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1707,13 +1719,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1722,16 +1734,16 @@
         <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1739,13 +1751,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1754,16 +1766,16 @@
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1771,13 +1783,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1786,16 +1798,16 @@
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1803,13 +1815,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
@@ -1818,16 +1830,16 @@
         <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -1835,13 +1847,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1850,16 +1862,16 @@
         <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1867,13 +1879,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1882,16 +1894,16 @@
         <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -1899,10 +1911,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>44</v>
@@ -1914,16 +1926,16 @@
         <v>76</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1931,13 +1943,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
@@ -1946,16 +1958,16 @@
         <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1963,13 +1975,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
@@ -1978,16 +1990,16 @@
         <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -1995,13 +2007,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
@@ -2010,16 +2022,16 @@
         <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -2027,13 +2039,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
@@ -2042,16 +2054,16 @@
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -2059,13 +2071,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -2074,16 +2086,16 @@
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -2091,13 +2103,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
@@ -2106,16 +2118,16 @@
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -2123,10 +2135,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>44</v>
@@ -2138,16 +2150,16 @@
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -2155,13 +2167,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -2170,16 +2182,16 @@
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -2187,31 +2199,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
         <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -2219,31 +2231,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>44</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="3">
-        <v>40</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="24">
@@ -2251,31 +2263,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
         <v>40</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="25">
@@ -2283,31 +2295,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>40</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>37</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -2315,31 +2327,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>37</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>34</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2392,7 +2404,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -2407,22 +2419,22 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2445,7 +2457,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>30</v>
@@ -2457,7 +2469,7 @@
         <v>47</v>
       </c>
       <c r="K2" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -2480,7 +2492,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2492,18 +2504,18 @@
         <v>52</v>
       </c>
       <c r="K3" s="3">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2512,33 +2524,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="K4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2547,33 +2559,33 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K5" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
@@ -2582,33 +2594,33 @@
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="K6" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
@@ -2617,33 +2629,33 @@
         <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K7" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
@@ -2652,33 +2664,33 @@
         <v>92</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2687,33 +2699,33 @@
         <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
@@ -2722,33 +2734,33 @@
         <v>88</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2757,33 +2769,33 @@
         <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="K11" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2792,30 +2804,30 @@
         <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>44</v>
@@ -2827,33 +2839,33 @@
         <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="K13" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
@@ -2862,33 +2874,33 @@
         <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K14" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
@@ -2897,33 +2909,33 @@
         <v>56</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="K15" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
@@ -2932,33 +2944,33 @@
         <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="K16" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="C17" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
@@ -2967,33 +2979,33 @@
         <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K17" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -3002,33 +3014,33 @@
         <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="K18" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
@@ -3037,30 +3049,30 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K19" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>44</v>
@@ -3072,33 +3084,33 @@
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="K20" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -3107,325 +3119,325 @@
         <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K21" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K22" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>44</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="3">
-        <v>40</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="K24" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>40</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>37</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="K25" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>37</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>34</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K26" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>34</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>30</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="K27" s="3">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>30</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>30</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="K28" s="3">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>30</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>30</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="K29" s="3">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>30</v>
@@ -3434,56 +3446,56 @@
         <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="K30" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>27</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="3">
-        <v>24</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="K31" s="3">
-        <v>84</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3492,45 +3504,45 @@
         <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>204</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>30</v>
@@ -3539,21 +3551,21 @@
         <v>205</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="K33" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3562,10 +3574,10 @@
         <v>23</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -3574,7 +3586,7 @@
         <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="K34" s="3">
         <v>23</v>
@@ -3582,13 +3594,13 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3597,33 +3609,33 @@
         <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="K35" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3632,33 +3644,33 @@
         <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="K36" s="3">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3667,68 +3679,68 @@
         <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="K37" s="3">
-        <v>79</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>23</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="3">
-        <v>20</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="K38" s="3">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3737,33 +3749,33 @@
         <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="K39" s="3">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3772,33 +3784,33 @@
         <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K40" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3807,68 +3819,68 @@
         <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K41" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>20</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="G42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>17</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="K42" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3877,33 +3889,33 @@
         <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="K43" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3915,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
@@ -3924,10 +3936,10 @@
         <v>260</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="K44" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -3935,10 +3947,10 @@
         <v>261</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3947,10 +3959,10 @@
         <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -3959,21 +3971,21 @@
         <v>263</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="K45" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3982,27 +3994,27 @@
         <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>87</v>
+        <v>267</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>269</v>
@@ -4017,19 +4029,19 @@
         <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="K47" s="3">
         <v>2</v>
@@ -4037,13 +4049,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4052,27 +4064,27 @@
         <v>17</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="K48" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>128</v>
+        <v>276</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>277</v>
@@ -4087,33 +4099,33 @@
         <v>17</v>
       </c>
       <c r="F49" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4122,10 +4134,10 @@
         <v>17</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
@@ -4134,10 +4146,10 @@
         <v>283</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>234</v>
+        <v>86</v>
       </c>
       <c r="K50" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -4145,80 +4157,80 @@
         <v>284</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>72</v>
+        <v>285</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F51" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="J51" s="3" t="s">
-        <v>288</v>
+        <v>237</v>
       </c>
       <c r="K51" s="3">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3">
         <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K52" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>67</v>
+        <v>246</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4227,103 +4239,103 @@
         <v>13</v>
       </c>
       <c r="F53" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="G54" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>10</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="K54" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>13</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>10</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="K55" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>67</v>
+        <v>305</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4332,33 +4344,33 @@
         <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>307</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>308</v>
+        <v>52</v>
       </c>
       <c r="K56" s="3">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4367,10 +4379,10 @@
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>30</v>
@@ -4379,21 +4391,21 @@
         <v>310</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="K57" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>128</v>
+        <v>312</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4402,33 +4414,33 @@
         <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>52</v>
+        <v>249</v>
       </c>
       <c r="K58" s="3">
-        <v>75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>314</v>
+        <v>127</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>315</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4440,7 +4452,7 @@
         <v>316</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>30</v>
@@ -4449,21 +4461,21 @@
         <v>317</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>318</v>
+        <v>52</v>
       </c>
       <c r="K59" s="3">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4472,68 +4484,68 @@
         <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>321</v>
+        <v>59</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>220</v>
+        <v>66</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>182</v>
+        <v>86</v>
       </c>
       <c r="K61" s="3">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>84</v>
+        <v>223</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4542,33 +4554,33 @@
         <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>327</v>
+        <v>203</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4577,33 +4589,33 @@
         <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="K63" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>329</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4612,19 +4624,19 @@
         <v>6</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="K64" s="3">
         <v>9</v>
@@ -4635,80 +4647,80 @@
         <v>333</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>93</v>
+        <v>334</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>335</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
       <c r="K65" s="3">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>337</v>
+        <v>92</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
+      <c r="G66" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="K66" s="3">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4720,7 +4732,7 @@
         <v>343</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>30</v>
@@ -4729,21 +4741,21 @@
         <v>344</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>345</v>
+        <v>243</v>
       </c>
       <c r="K67" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>346</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>84</v>
+        <v>223</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4755,7 +4767,7 @@
         <v>347</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>30</v>
@@ -4764,21 +4776,21 @@
         <v>348</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>345</v>
+        <v>151</v>
       </c>
       <c r="K68" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4787,22 +4799,22 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I69" s="3" t="s">
+      <c r="J69" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="K69" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
@@ -4813,7 +4825,7 @@
         <v>354</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4822,59 +4834,94 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>308</v>
+        <v>105</v>
       </c>
       <c r="K70" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>358</v>
+        <v>258</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E71" s="3">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>355</v>
+      </c>
       <c r="G71" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>359</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="K71" s="3">
-        <v>9</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K72" s="3">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K71"/>
+  <autoFilter ref="A1:K72"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4946,6 +4993,7 @@
     <hyperlink ref="I69" r:id="rId68"/>
     <hyperlink ref="I70" r:id="rId69"/>
     <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4953,8 +5001,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4976,10 +5024,10 @@
         <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>41</v>
@@ -4987,175 +5035,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>90</v>
+        <v>297</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>298</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>199</v>
+        <v>345</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>200</v>
+        <v>346</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>348</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5170,178 +5122,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3">
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>286</v>
+        <v>350</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>347</v>
+        <v>289</v>
       </c>
       <c r="B9" s="3">
         <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3">
         <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3">
         <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B13" s="3">
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -5361,10 +5313,10 @@
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
@@ -5375,7 +5327,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3">
@@ -5383,10 +5335,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -5397,7 +5349,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
@@ -5408,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -5429,13 +5381,13 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -5446,7 +5398,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5455,22 +5407,22 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D4" s="3"/>
     </row>
